--- a/A股短线选股筛选条件.xlsx
+++ b/A股短线选股筛选条件.xlsx
@@ -159,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -202,6 +202,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -577,9 +595,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>A股短线选股筛选条件 — v6.4.13</t>
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>A股短线选股筛选条件 — v6.4.20</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr"/>
@@ -591,12 +609,12 @@
           <t>版本号</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>v6.4.13</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>v6.4.20</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>2026-06-12更新</t>
         </is>
@@ -1060,6 +1078,40 @@
       <c r="C30" s="4" t="inlineStr">
         <is>
           <t>新增步骤零</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>v6.4.14</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>全面漏洞审计修复：20项问题（高5/中6/低9），参数化+健壮性+章节编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>v6.4.20</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>GitHub推送前自动同步</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1250,148 +1302,126 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4C</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>持仓跟踪同步</t>
+          <t>持仓危机检查</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>收盘价同步</t>
+          <t>跌停/浮亏&gt;15%/L1触发</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>更新持仓跟踪.xlsx</t>
+          <t>对话置顶告警</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>4C</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>持仓危机检查</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>跌停/浮亏&gt;15%/L1触发</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>对话置顶告警</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>开盘前</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>期货跌&gt;1%</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>降档</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>开盘前</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>期货跌&gt;1%</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>降档</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>持仓同步</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>遍历holding搜收盘价</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>更新pnl_pct</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>持仓同步</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>遍历holding搜收盘价</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>更新pnl_pct</t>
-        </is>
-      </c>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>历史持久化</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>损坏→v6.4.13</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>历史持久化</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>7日推荐排除+90日清理</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>文件初始化</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>策略调整记录末条</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>损坏→v6.4.4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>文件初始化</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>策略调整记录末条</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>损坏→v6.4.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>财报季</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>1/3/4/8/10月</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>事件×1.5+仓位+5%</t>
         </is>
@@ -1416,9 +1446,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>关键纪律 — v6.4.13</t>
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>关键纪律 — v6.4.20</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr"/>
@@ -1578,39 +1608,37 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>T+1兑现率&lt;30%→自动降档</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>v6.4.4新增</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>筛选条件变化时同步更新本文件并推送GitHub</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>v6.4.13</t>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>筛选条件变化时同步更新本文件（仅本地）</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>v6.4.14</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="22" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -2225,14 +2253,14 @@
           <t>近20日跌幅&gt;30%且无基本面改善</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>数据不可达→跳过</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>正常排除</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3069,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>北向3日连净买+主力&gt;3000万+涨&lt;2%</t>
+          <t>北向3日连净买+主力&gt;{northbound_threshold}万+涨&lt;2%</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -3066,7 +3094,7 @@
           <t>E 回调企稳</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>20日新高+回调MA20±3%+连3日缩量+站回MA5放量(量&gt;昨×1.3)</t>
         </is>
@@ -3591,7 +3619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4034,104 +4062,72 @@
       </c>
       <c r="D25" s="4" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>兑现率&lt;{conversion_rate_threshold*100}%</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>近{conversion_rate_window_days}日兑现率&lt;{conversion_rate_threshold*100}%</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>处置</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>九.C、T+1兑现率闭环 — v6.4.4新增</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="15" t="n"/>
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>连续{conversion_rate_consecutive_days}日&lt;{conversion_rate_threshold*100}%</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>连续{conversion_rate_consecutive_days}个交易日</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>暂停推荐1天</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>极端保护</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>条件</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>阈值</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>处置</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>兑现率&lt;30%</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>近10日兑现率&lt;30%</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>降一档仓位(强→震→弱→跳过)</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>自动收缩</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>连续3日&lt;30%</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>连续3个交易日</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>暂停推荐1天</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>极端保护</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>兑现率≥60%</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr"/>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>兑现率≥{conversion_rate_restore*100}%</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>恢复至正常档位</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>自动恢复</t>
         </is>
       </c>
     </row>
+    <row r="29" ht="22" customHeight="1"/>
+    <row r="30" ht="22" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A27:D27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/A股短线选股筛选条件.xlsx
+++ b/A股短线选股筛选条件.xlsx
@@ -597,7 +597,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>A股短线选股筛选条件 — v6.4.20</t>
+          <t>A股短线选股筛选条件 — v6.5.1</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>v6.4.20</t>
+          <t>v6.5.1</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12更新</t>
+          <t>2026-06-13更新</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>关键纪律 — v6.4.20</t>
+          <t>关键纪律 — v6.5.1</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr"/>
